--- a/home/data/위험성평가_기본데이터.xlsx
+++ b/home/data/위험성평가_기본데이터.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RT" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,23 +12,34 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컨테이너" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,8 +51,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-        <bgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,7 +73,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,14 +436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -983,6 +992,210 @@
         <is>
           <t>1. 웰딩하우스 돌출 부위 야광 완충재 부착
 2. 철수 시에도 안전모 미착용 절대 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>가이드튜브 꺾임, 장비 결함 등으로 동위원소 선원 미회수 시 고선량 피폭 위험</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>장비 육안 점검 / 작업 전 TBM 전파</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1. 현장에 비상용 롱 텅(Handling tong) 및 납 차폐체 상시 비치
+2. 비상사태 발생 시 방사선안전관리자 즉시 보고 및 비상대응 매뉴얼 숙지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>야간 검사 시 조명 부족 및 시야 미확보로 인한 전도, 추락, 장비 충돌 위험</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>개인용 랜턴 지급 / 주의 전파</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1. 검사 구역 및 주요 이동 통로에 30 Lux 이상의 가설 투광기 추가 설치
+2. 작업자 전원 고휘도 반사조끼 착용 및 야광 테이프로 걸림 위험 부위 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>배관 내부 및 깊은 트렌치 내부 출입 시 산소 결핍 또는 유해가스 체류로 인한 질식</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>출입 전 복합가스 농도 측정</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1. 작업 중 복합가스농도측정기(O2, CO, H2S, LEL) 상시 휴대 및 알람 설정
+2. 깊은 굴착 부위 작업 시 송풍기를 이용한 강제 환기 및 외부 감시인 배치</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>야간 조명등 및 검사장비 케이블 피복 손상, 누전, 우천 시 감전 위험</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>전선 정리 / 우천 시 작업 통제</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1. 현장 내 모든 임시 가설전기는 누전차단기(30mA)를 거쳐서 사용
+2. 피복 손상 케이블 즉각 폐기 및 전선 가공(바닥 띄움) 거치 실시</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>야간 암실 차량 주·정차 및 이동 시 시야 확보 불량으로 근로자 및 타 장비 충돌</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>지정 구역 주차 및 유도자 배치</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1. 암실차 주·정차 위치 주변에 안전 라바콘 및 점멸등(윙카) 설치로 시야 확보
+2. 차량 후진 및 좁은 구역 이동 시 반드시 전담 신호수 유도 하에 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>작업 후 정리</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>차량 이동 중 동위원소 저장용기 전도/낙하로 인한 방사능 유출 및 장비 파손</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>전용 운반차량 사용 및 고정</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1. 차량 내 저장용기 이중 시건장치 결속 및 와이어로프로 차체에 단단히 고정
+2. 운송 중 과속/급정거 엄금 및 방사선 경고 표지 차량 4면 부착</t>
         </is>
       </c>
     </row>
@@ -998,13 +1211,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1398,13 +1610,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1866,13 +2077,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>

--- a/home/data/위험성평가_기본데이터.xlsx
+++ b/home/data/위험성평가_기본데이터.xlsx
@@ -1,45 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컨테이너" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="컨테이너" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -51,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -437,12 +427,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -497,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 정리정돈</t>
+          <t>개인 랜턴으로 통로 조도 확보 / 바닥 장애물 사전 제거</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -531,7 +522,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안전모 착용 / 작업 전 TBM 전파</t>
+          <t>안전모 착용 / 2인 1조 작업 / 아웃트리거 사용</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -565,7 +556,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>작업 전 TBM 전파</t>
+          <t>중장비 선회 반경 내 절대 접근 금지 및 우회 통행 철저</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -581,8 +572,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. 중장비 작업 반경 내 근로자 절대 출입 금지
-2. 전담 신호수 배치 및 운전원 무전기 소통 확립</t>
+          <t>1. 중장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
+2. 부득이하게 장비 주변 이동 시 운전원과 Eye Contact 및 수신호 교환</t>
         </is>
       </c>
     </row>
@@ -599,7 +590,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 점검</t>
+          <t>안전대 체결 불가 시 작업화 이물질 제거 및 2인 1조 밀착 통제</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -615,7 +606,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1. 2m 이상 고소작업 시 지정된 생명줄에 안전대 체결 필수
+          <t>1. 배관 탑승 시 하부에서 1인이 지속 모니터링 및 밀착 지지
 2. 우천/결빙 시 배관 상부 탑승 작업 전면 중지</t>
         </is>
       </c>
@@ -633,7 +624,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용</t>
+          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 점검 및 제거</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -667,7 +658,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보호구 착용 / 점검</t>
+          <t>최상단 탑승 금지 자체 확인 / 사다리 2인 1조 작업(1인 지지)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -701,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>보호구 착용 / 점검</t>
+          <t>납 차폐체 이동 시 전용 대차 사용 / 2인 이상 협력하여 운반</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -735,7 +726,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>작업 전 TBM 전파</t>
+          <t>인양 전 슬링벨트 상태 육안 점검 및 결속부 2중 자체 확인</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -769,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안전모 착용 / 점검</t>
+          <t>작업 전 슬링벨트 자체 점검(손상품 즉시 폐기) 및 2줄 걸이 결속 확인</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -803,7 +794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>보호구 착용 / TBM 전파</t>
+          <t>작업 전후 스트레칭 및 중량물 취급 시 올바른 자세 유지</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -837,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>안전모 착용 / 점검</t>
+          <t>진입 전 굴착 법면 균열 및 용수(물비침) 육안 점검</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -871,7 +862,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>보호구 착용 / 특별교육</t>
+          <t>작업 전 방독마스크, 내화학 장갑 자체 착용 상태 교차 점검</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -940,7 +931,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>보호구 착용 / TBM 전파</t>
+          <t>해체 자재는 하부 조원에게 직접 수작업 인계 / 자재 투척 절대 금지</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -956,8 +947,8 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1. 정리 작업 중에도 안전대 체결 및 안전모 턱끈 결속 유지
-2. 해체된 자재는 던지지 않고 로프나 포대 등을 이용해 하강</t>
+          <t>1. 배관 하강 완료 전까지 안전모 턱끈 결속 유지
+2. 해체된 자재는 2인 1조로 안전하게 수작업 인계 및 던지기 엄금</t>
         </is>
       </c>
     </row>
@@ -974,7 +965,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>보호구 착용 / TBM 전파</t>
+          <t>진입 전 헤드랜턴으로 상부 장애물 사전 확인 및 안전모 턱끈 결속 철저</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -990,7 +981,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1. 웰딩하우스 돌출 부위 야광 완충재 부착
+          <t>1. 웰딩하우스 진입 전 헤드랜턴으로 상부 돌출물 육안 확인
 2. 철수 시에도 안전모 미착용 절대 금지</t>
         </is>
       </c>
@@ -1008,7 +999,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>장비 육안 점검 / 작업 전 TBM 전파</t>
+          <t>장비 육안 점검 / 현장에 비상용 롱 텅(Handling tong) 사전 비치</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1042,7 +1033,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인용 랜턴 지급 / 주의 전파</t>
+          <t>헤드랜턴 및 고휘도 반사조끼 착용</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1076,7 +1067,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>출입 전 복합가스 농도 측정</t>
+          <t>배관 내부 인력 진입 절대 금지(크롤러 장비 대체) / 트렌치 진입 전 복합가스 자체 측정</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1092,8 +1083,8 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1. 작업 중 복합가스농도측정기(O2, CO, H2S, LEL) 상시 휴대 및 알람 설정
-2. 깊은 굴착 부위 작업 시 송풍기를 이용한 강제 환기 및 외부 감시인 배치</t>
+          <t>1. 배관 내부 진입 절대 금지 및 크롤러 등 장비로 대체
+2. 트렌치 진입 전 복합가스 측정 및 외부 감시인 배치</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>전선 정리 / 우천 시 작업 통제</t>
+          <t>누전차단기 부착형 릴선 전용 사용 및 손상된 케이블 즉시 폐기</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1127,7 +1118,7 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>1. 현장 내 모든 임시 가설전기는 누전차단기(30mA)를 거쳐서 사용
-2. 피복 손상 케이블 즉각 폐기 및 전선 가공(바닥 띄움) 거치 실시</t>
+2. 피복 손상 케이블 즉각 폐기 및 바닥 띄움 거치 실시</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1135,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>지정 구역 주차 및 유도자 배치</t>
+          <t>동승자 하차 후 신호봉 자체 직접 차량 유도</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1160,8 +1151,8 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1. 암실차 주·정차 위치 주변에 안전 라바콘 및 점멸등(윙카) 설치로 시야 확보
-2. 차량 후진 및 좁은 구역 이동 시 반드시 전담 신호수 유도 하에 이동</t>
+          <t>1. 암실차 주·정차 시 점멸등(윙카) 작동 및 작업자 고휘도 반사조끼 착용
+2. 야간 차량 후진 및 좁은 구역 이동 시 동승자(작업자)가 하차하여 신호봉으로 직접 유도</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1169,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>전용 운반차량 사용 및 고정</t>
+          <t>차량 내 저장용기 자체 이중 시건장치 확인</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1211,12 +1202,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1271,7 +1263,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 확인 및 제거</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1300,29 +1292,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>손상된 슬링벨트 사용 시 판단에 의한 중량물낙하 사고 위험</t>
+          <t>소형 장비(탐상기 등) 수작업 운반 중 계단/비계에서 추락 및 전도</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>전용 수납가방 활용으로 양손 확보 및 3점 지지 승강 철저</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. 작업 전 슬링벨트 손상 및 규격 확인
-2. 파손된 슬링벨트는 현장에서 즉시 파기 및 교체</t>
+          <t>1. 장비 전용 수납가방 사용으로 이동 시 양손 확보
+2. 사다리/비계 승강 시 3점 지지 철저</t>
         </is>
       </c>
     </row>
@@ -1334,29 +1326,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>중량물 줄걸이작업 부적합 시 낙하에 의한 사고위험</t>
+          <t>배관 상부 등 고소작업 시 소형 장비(탐상기, 겔 등) 하부 낙하</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>장비 낙하방지끈 체결 및 하부 작업자 접근 통제</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. 지정된 줄걸이 용구 사용 및 결속 상태 교차 점검
-2. 관리감독자(또는 신호수) 지휘 하에 안전하게 인양 진행</t>
+          <t>1. 배관 탑승 작업 시 탐상기 및 공구 낙하방지끈 체결
+2. 작업 구역 하부 근로자 접근 전면 통제</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1365,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>현장 투입 전 개인보호구 착용 및 안전모 턱끈 자체 체결 확인</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1402,12 +1394,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>중장비 이용 중량물 취급 작업 중 신호오류에 의한 충돌사고 위험</t>
+          <t>중장비 주변 이동 중 장비와 충돌 또는 끼임</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>운전원과 직접 Eye Contact 및 수신호 교환 후 통행</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1423,8 +1415,8 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1. 장비 작업 반경 내 출입 통제 및 펜스 설치
-2. 전담 신호수 배치 및 운전원 간 무전 소통 확립</t>
+          <t>1. 장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
+2. 부득이하게 장비 주변 이동 시 운전원과 눈맞춤 및 수신호 확인 필수</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1467,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1504,12 +1496,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>중량물 줄걸이작업 부적합 시 낙하에 의한 사고위험</t>
+          <t>검사 완료 후 장비 반출 시 계단/비계에서 추락 및 전도</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>장비 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1520,13 +1512,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1. 탐상 장비 반출 시에도 2줄 걸이 이상 결속 원칙 준수
-2. 인양물 하부 접근 절대 금지</t>
+          <t>1. 반출 시 장비를 손에 쥐고 이동하는 행위 절대 금지
+2. 전용 가방 수납 후 3점 지지 하강 원칙 준수</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1530,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>손상된 슬링벨트 사용 시 판단에 의한 중량물낙하 사고 위험</t>
+          <t>장비 반출 중 수작업 인계 시 하부로 장비 낙하</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>하부 조원에게 직접 수작업 인계 및 장비 투척 절대 금지</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1554,13 +1546,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1. 철수 작업 전 슬링벨트 훼손 유무 재차 확인
-2. 손상 의심 시 무리한 재사용 금지 및 즉각 폐기</t>
+          <t>1. 2인 1조 작업으로 하부 조원에게 안전하게 수작업 인계
+2. 장비를 바닥으로 휙 던지는 행위 절대 금지</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1564,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>중장비 이용 중량물 취급 작업 중 신호오류에 의한 충돌사고 위험</t>
+          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1593,8 +1585,8 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1. 장비 철수 동선 사전 파악 및 신호수/유도자 통제
-2. 운전원과 수신호 및 무전 교신 확인 후 이동</t>
+          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
+2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1602,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1670,7 +1663,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 확인 및 제거</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1699,29 +1692,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>손상된 슬링벨트 사용 시 판단에 의한 중량물낙하 사고 위험</t>
+          <t>소형 자재(스프레이, 세척액 등) 수작업 운반 중 추락/전도</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>전용 수납가방 활용으로 양손 확보 및 3점 지지 승강 철저</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. 작업 전 슬링벨트 손상 및 규격 확인
-2. 파손된 슬링벨트는 현장에서 즉시 파기 및 교체</t>
+          <t>1. 스프레이 등 탐상 자재 전용 포켓/가방에 수납
+2. 사다리/비계 승강 시 3점 지지 철저</t>
         </is>
       </c>
     </row>
@@ -1733,29 +1726,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>중량물 줄걸이작업 부적합 시 낙하에 의한 사고위험</t>
+          <t>배관 상부 등 고소작업 시 스프레이 캔 하부 낙하</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>작업 구역 하부 접근 통제 및 잔여 자재 안전한 곳에 비치</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. 지정된 줄걸이 용구 사용 및 결속 상태 교차 점검
-2. 관리감독자(또는 신호수) 지휘 하에 안전하게 인양 진행</t>
+          <t>1. 비계나 배관 위 작업 시 스프레이가 굴러떨어지지 않도록 조치
+2. 하부 근로자 통행 전면 금지</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1765,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>현장 투입 전 개인보호구 착용 및 안전모 턱끈 자체 체결 확인</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1801,12 +1794,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>중장비 이용 중량물 취급 작업 중 신호오류에 의한 충돌사고 위험</t>
+          <t>중장비 주변 이동 중 장비와 충돌 또는 끼임</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>운전원과 직접 Eye Contact 및 수신호 교환 후 통행</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1822,8 +1815,8 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1. 장비 작업 반경 내 출입 통제 및 펜스 설치
-2. 전담 신호수 배치 및 운전원 간 무전 소통 확립</t>
+          <t>1. 장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
+2. 부득이하게 장비 주변 이동 시 운전원과 눈맞춤 및 수신호 확인 필수</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1833,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MSDS 준수 보호구 착용</t>
+          <t>침투탐상제 취급 전 MSDS 유해성 자체 숙지 및 전파</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1874,7 +1867,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MSDS 준수 보호구 착용</t>
+          <t>화학물질 취급 전 내화학 장갑/마스크 자체 수령 및 착용</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1942,7 +1935,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1971,12 +1964,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>중량물 줄걸이 작업 부적합 시 낙하에 의한 사고위험</t>
+          <t>검사 완료 후 자재 반출 시 계단/비계에서 추락 및 전도</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>자재를 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1987,13 +1980,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1. 자재 반출 시에도 2줄 걸이 이상 결속 원칙 준수
-2. 인양물 하부 절대 접근 금지</t>
+          <t>1. 다 쓴 스프레이 캔 등을 손에 쥐고 이동 금지
+2. 빈 캔은 가방에 회수 후 3점 지지 하강 원칙 준수</t>
         </is>
       </c>
     </row>
@@ -2005,12 +1998,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>손상된 슬링벨트 사용 시 판단에 의한 중량물낙하 사고 위험</t>
+          <t>자재 반출 중 수작업 인계 시 하부로 스프레이 캔 낙하</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>하부 조원에게 직접 수작업 인계 및 폐캔 투척 절대 금지</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2021,13 +2014,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1. 철수 작업 전 슬링벨트 훼손 유무 재차 확인
-2. 손상 의심 시 무리한 사용 금지 및 즉각 폐기</t>
+          <t>1. 하부 조원에게 빈 캔을 건네줄 때 안전하게 손으로 인계
+2. 사용이 끝난 빈 캔 바닥 투척 절대 금지</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2032,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>중장비 이용 중량물 취급 작업 중 신호오류에 의한 충돌사고 위험</t>
+          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>안전모, 안전화 착용 / 작업 전 점검</t>
+          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2060,8 +2053,8 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1. 장비 철수 동선 사전 파악 및 신호수/유도자 통제
-2. 운전원과 수신호 및 무전 교신 확인 후 이동</t>
+          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
+2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2070,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2137,7 +2131,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안전모 착용 / 작업 전 점검</t>
+          <t>작업 전 슬링벨트 자체 점검(손상품 즉시 폐기) 및 4줄 걸이 결속 확인</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2205,7 +2199,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>절연장갑 착용 / TBM 전파</t>
+          <t>전원 연결부 자체 접지 상태 육안 확인 및 누전차단기 테스트</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2222,7 +2216,7 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>1. 메인 분전반 내 누전차단기 설치 및 정상 작동 여부 확인
-2. 가설전기 외함 접지(3종) 실시 및 전선 거치대 사용</t>
+2. 가설전기 외함 접지(3종) 실시 및 전선 바닥 띄움 거치</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2267,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>작업 전 점검</t>
+          <t>미끄럼 방지 테이프 자체 확인 및 결빙 시 제설 조치 철저</t>
         </is>
       </c>
       <c r="D6" t="n">

--- a/home/data/위험성평가_기본데이터.xlsx
+++ b/home/data/위험성평가_기본데이터.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -478,439 +478,507 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>필름부착 작업 시 배관상부에서 미끄러져 넘어짐 위험</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>안전대 체결 불가 시 작업화 이물질 제거 및 2인 1조 밀착 통제</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1. 배관 탑승 시 하부에서 1인이 지속 모니터링 및 밀착 지지
+2. 우천/결빙 시 배관 상부 탑승 작업 전면 중지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지하(트렌치) 작업 중 상부 낙하물에 의한 사고위험</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 점검 및 제거</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1. 굴착 상단부에 자재 및 공구 적재 금지
+2. 하부 작업 시 상부 타 공정 동시 작업 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>필름부착작업 시 사다리 작업 중 추락/전도 위험</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>최상단 탑승 금지 자체 확인 / 사다리 2인 1조 작업(1인 지지)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1. A형 사다리 최상단 발판 탑승 절대 금지
+2. 1인 하단부 지지 (2인 1조 작업)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>인소스로봇(크롤러) 투입/반출 작업 시 낙하 위험</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>인양 전 슬링벨트 상태 육안 점검 및 결속부 2중 자체 확인</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1. 투입 전용 인양 장비 사용 및 결속 상태 2중 확인
+2. 배터리 및 조작계 이상 시 배관 내부 인력 투입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>손상된 슬링벨트 사용 및 줄걸이 부적합으로 낙하 사고 위험</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>작업 전 슬링벨트 자체 점검(손상품 즉시 폐기) 및 2줄 걸이 결속 확인</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1. 작업 전 슬링벨트 손상 규격 확인 및 파손품 폐기
+2. 관리감독자 지휘 하에 안전하게 인양 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차폐체 설치/해체 작업 시 중량물 낙하에 의한 사고 위험</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>납 차폐체 수작업 이동 시 반드시 2인 1조 협력 운반 및 작업화(안전화) 착용 상태 점검</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1. 100kg 이상 인양 시 2줄 걸이 이상 결속
+2. 인양 중인 중량물 하부 통행 전면 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>협소공간 필름부착 시 부자연스런 자세에 의한 근골격계질환</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>작업 전후 스트레칭 및 중량물 취급 시 올바른 자세 유지</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1. 작업 전·후 스트레칭 실시 및 중량물 인양 올바른 자세 교육
+2. 장시간 작업 시 교대 및 휴식 시간 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>우천 등으로 인한 굴착법면 상태 약화로 붕괴 위험</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>진입 전 굴착 법면 균열 및 용수(물비침) 육안 점검</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 점검
+2. 호우 경보 발효 시 굴착 지점 내부 진입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>배관 내부 및 깊은 트렌치 내부 출입 시 산소 결핍 또는 유해가스 체류로 인한 질식</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>배관 내부 인력 진입 절대 금지(크롤러 장비 대체) / 트렌치 진입 전 복합가스 자체 측정</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1. 배관 내부 진입 절대 금지 및 크롤러 등 장비로 대체
+2. 트렌치 진입 전 복합가스 측정 및 외부 감시인 배치</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>이동</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>이동 중 지면 단차, 돌출물, 자재 등에 걸려 넘어짐 (전도) 위험</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>개인 랜턴으로 통로 조도 확보 / 바닥 장애물 사전 제거</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>1. 가설계단 및 이동통로 내 자재 정리정돈 철저
 2. 조도(밝기) 확보 및 보행 중 스마트폰 사용 금지 전파</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>이동</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>이동용 사다리를 이용한 고소 이동 중 사다리 전도 및 추락</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>안전모 착용 / 2인 1조 작업 / 아웃트리거 사용</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>1. 사다리 상단 고정 및 아웃트리거 전개 확인
 2. 사다리 이용 시 반드시 2인 1조 작업</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>이동</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>현장 내 중장비(굴착기 등) 주변 이동 중 장비와 충돌 또는 끼임</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>중장비 선회 반경 내 절대 접근 금지 및 우회 통행 철저</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>1. 중장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
 2. 부득이하게 장비 주변 이동 시 운전원과 Eye Contact 및 수신호 교환</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>필름부착 작업 시 배관상부에서 미끄러져 넘어짐 위험</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>안전대 체결 불가 시 작업화 이물질 제거 및 2인 1조 밀착 통제</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1. 배관 탑승 시 하부에서 1인이 지속 모니터링 및 밀착 지지
-2. 우천/결빙 시 배관 상부 탑승 작업 전면 중지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>지하(트렌치) 작업 중 상부 낙하물에 의한 사고위험</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 점검 및 제거</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1. 굴착 상단부에 자재 및 공구 적재 금지
-2. 하부 작업 시 상부 타 공정 동시 작업 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>필름부착작업 시 사다리 작업 중 추락/전도 위험</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>최상단 탑승 금지 자체 확인 / 사다리 2인 1조 작업(1인 지지)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1. A형 사다리 최상단 발판 탑승 절대 금지
-2. 1인 하단부 지지 (2인 1조 작업)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>차폐체 설치/해체 작업 시 중량물 낙하에 의한 사고 위험</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>납 차폐체 이동 시 전용 대차 사용 / 2인 이상 협력하여 운반</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1. 100kg 이상 인양 시 2줄 걸이 이상 결속
-2. 인양 중인 중량물 하부 통행 전면 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>인소스로봇(크롤러) 투입/반출 작업 시 낙하 위험</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>인양 전 슬링벨트 상태 육안 점검 및 결속부 2중 자체 확인</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1. 투입 전용 인양 장비 사용 및 결속 상태 2중 확인
-2. 배터리 및 조작계 이상 시 배관 내부 인력 투입 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>손상된 슬링벨트 사용 및 줄걸이 부적합으로 낙하 사고 위험</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>작업 전 슬링벨트 자체 점검(손상품 즉시 폐기) 및 2줄 걸이 결속 확인</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1. 작업 전 슬링벨트 손상 규격 확인 및 파손품 폐기
-2. 관리감독자 지휘 하에 안전하게 인양 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>협소공간 필름부착 시 부자연스런 자세에 의한 근골격계질환</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>작업 전후 스트레칭 및 중량물 취급 시 올바른 자세 유지</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1. 작업 전·후 스트레칭 실시 및 중량물 인양 올바른 자세 교육
-2. 장시간 작업 시 교대 및 휴식 시간 부여</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>우천 등으로 인한 굴착법면 상태 약화로 붕괴 위험</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>진입 전 굴착 법면 균열 및 용수(물비침) 육안 점검</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 점검
-2. 호우 경보 발효 시 굴착 지점 내부 진입 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>필름 현상 작업 시 약품 취급 오류/누출에 의한 흡입 및 화상 위험</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>작업 전 방독마스크, 내화학 장갑 자체 착용 상태 교차 점검</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1. 현상액/정착액 MSDS(물질안전보건자료) 비치 및 교육
-2. 작업 시 방독마스크, 내화학 장갑 착용 철저</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>이동</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>야간 암실 차량 주·정차 및 이동 시 시야 확보 불량으로 근로자 및 타 장비 충돌</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>동승자 하차 후 신호봉 자체 직접 차량 유도</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1. 암실차 주·정차 시 점멸등(윙카) 작동 및 작업자 고휘도 반사조끼 착용
+2. 야간 차량 후진 및 좁은 구역 이동 시 동승자(작업자)가 하차하여 신호봉으로 직접 유도</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>비파괴검사</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>야간 검사 시 조명 부족 및 시야 미확보로 인한 전도, 추락, 장비 충돌 위험</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>헤드랜턴 및 고휘도 반사조끼 착용</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1. 검사 구역 및 주요 이동 통로에 30 Lux 이상의 가설 투광기 추가 설치
+2. 작업자 전원 고휘도 반사조끼 착용 및 야광 테이프로 걸림 위험 부위 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>검사안전구역 미설정 및 통제 부실 시 방사능 노출 피폭 위험</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>출입금지 간판 설치</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>1. 콜리메이터(차폐장비) 필수 장착으로 선량 최소화
 2. 방사선 10μSv/hr 이하 통제구역 설정 및 전담 감시자 배치
@@ -918,275 +986,417 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>가이드튜브 꺾임, 장비 결함 등으로 동위원소 선원 미회수 시 고선량 피폭 위험</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>장비 육안 점검 / 현장에 비상용 롱 텅(Handling tong) 사전 비치</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1. 현장에 비상용 롱 텅(Handling tong) 및 납 차폐체 상시 비치
+2. 비상사태 발생 시 방사선안전관리자 즉시 보고 및 비상대응 매뉴얼 숙지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>방사선 작업종사자 건강검진 미실시 및 피폭선량 기록 누락으로 과피폭 위험</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>방사선 작업종사자 건강검진 결과서 현장 비치 확인</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1. 방사선 작업종사자 건강검진 결과서 현장 비치 및 주기적 갱신
+2. 개인선량계 패용 및 월별 피폭선량 기록·관리 철저
+3. ALARA 원칙 준수: 거리·차폐·시간 3원칙 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>서베이미터 미소지 또는 교정주기 초과 장비 사용으로 인한 방사선량 측정 오류 및 대피 지연</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>작업 전 서베이미터 정상 작동(배터리) 및 교정 유효기간 점검</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1. 현장 투입 전 서베이미터 작동 상태 일일 점검
+2. 검·교정 유효기간 초과 장비 절대 사용 금지
+3. 작업 중 상시 서베이미터 전원 ON 상태 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>방사선 투과 검사 진행 중 경고등(경광등) 미작동 및 감시 소홀로 인한 타 공정 근로자 통제구역 오진입</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>경광등 작동 확인 및 타 공정 작업자 접근 통제</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1. 선원 노출 시 경광등(회전 점멸등)이 즉각 작동되도록 사전 테스트
+2. 교차로 및 사각지대에 통제 인원 추가 배치
+3. 타 공정 근로자 대상 방사선 작업 시간 및 구역 사전 공지 전파</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>야간 조명등 및 검사장비 케이블 피복 손상, 누전, 우천 시 감전 위험</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>누전차단기 부착형 릴선 전용 사용 및 손상된 케이블 즉시 폐기</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1. 현장 내 모든 임시 가설전기는 누전차단기(30mA)를 거쳐서 사용
+2. 피복 손상 케이블 즉각 폐기 및 바닥 띄움 거치 실시</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>필름 현상 작업 시 약품 취급 오류/누출에 의한 흡입 및 화상 위험</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>작업 전 방독마스크, 내화학 장갑 자체 착용 상태 교차 점검</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1. 현상액/정착액 MSDS(물질안전보건자료) 비치 및 교육
+2. 작업 시 방독마스크, 내화학 장갑 착용 철저</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>콜리메이터(차폐체) 미사용 또는 파손품 사용으로 인한 방사선 과다 누출 및 주변 피폭</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>콜리메이터 장착 상태 확인</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1. 투과 검사 시 콜리메이터 장착 의무화 (미장착 작업 절대 금지)
+2. 작업 전 콜리메이터 파손 및 변형 여부 육안 점검
+3. 현장 여건상 통제 반경이 부족할 경우 추가 납 차폐막 설치</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>작업 후 정리</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>필름 및 차폐체 해체 작업 시 배관상부 미끄러짐 및 추락/낙하</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>해체 자재는 하부 조원에게 직접 수작업 인계 / 자재 투척 절대 금지</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>1. 배관 하강 완료 전까지 안전모 턱끈 결속 유지
 2. 해체된 자재는 2인 1조로 안전하게 수작업 인계 및 던지기 엄금</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>작업 후 정리</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>웰딩하우스 하부 및 현장 정리 중 두부 충돌 및 부딪힘 위험</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>진입 전 헤드랜턴으로 상부 장애물 사전 확인 및 안전모 턱끈 결속 철저</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>1. 웰딩하우스 진입 전 헤드랜턴으로 상부 돌출물 육안 확인
 2. 철수 시에도 안전모 미착용 절대 금지</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>가이드튜브 꺾임, 장비 결함 등으로 동위원소 선원 미회수 시 고선량 피폭 위험</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>장비 육안 점검 / 현장에 비상용 롱 텅(Handling tong) 사전 비치</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>작업 후 정리</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>차량 이동 중 동위원소 저장용기 전도/낙하로 인한 방사능 유출 및 장비 파손</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>차량 내 저장용기 자체 이중 시건장치 확인</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1. 현장에 비상용 롱 텅(Handling tong) 및 납 차폐체 상시 비치
-2. 비상사태 발생 시 방사선안전관리자 즉시 보고 및 비상대응 매뉴얼 숙지</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>야간 검사 시 조명 부족 및 시야 미확보로 인한 전도, 추락, 장비 충돌 위험</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>헤드랜턴 및 고휘도 반사조끼 착용</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1. 검사 구역 및 주요 이동 통로에 30 Lux 이상의 가설 투광기 추가 설치
-2. 작업자 전원 고휘도 반사조끼 착용 및 야광 테이프로 걸림 위험 부위 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>배관 내부 및 깊은 트렌치 내부 출입 시 산소 결핍 또는 유해가스 체류로 인한 질식</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>배관 내부 인력 진입 절대 금지(크롤러 장비 대체) / 트렌치 진입 전 복합가스 자체 측정</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1. 배관 내부 진입 절대 금지 및 크롤러 등 장비로 대체
-2. 트렌치 진입 전 복합가스 측정 및 외부 감시인 배치</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>야간 조명등 및 검사장비 케이블 피복 손상, 누전, 우천 시 감전 위험</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>누전차단기 부착형 릴선 전용 사용 및 손상된 케이블 즉시 폐기</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1. 현장 내 모든 임시 가설전기는 누전차단기(30mA)를 거쳐서 사용
-2. 피복 손상 케이블 즉각 폐기 및 바닥 띄움 거치 실시</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>이동</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>야간 암실 차량 주·정차 및 이동 시 시야 확보 불량으로 근로자 및 타 장비 충돌</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>동승자 하차 후 신호봉 자체 직접 차량 유도</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1. 암실차 주·정차 시 점멸등(윙카) 작동 및 작업자 고휘도 반사조끼 착용
-2. 야간 차량 후진 및 좁은 구역 이동 시 동승자(작업자)가 하차하여 신호봉으로 직접 유도</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>작업 후 정리</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>차량 이동 중 동위원소 저장용기 전도/낙하로 인한 방사능 유출 및 장비 파손</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>차량 내 저장용기 자체 이중 시건장치 확인</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>1. 차량 내 저장용기 이중 시건장치 결속 및 와이어로프로 차체에 단단히 고정
 2. 운송 중 과속/급정거 엄금 및 방사선 경고 표지 차량 4면 부착</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>폭염 시 야외 작업 중 열사병·열탈진 등 온열질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 폭염 특보 확인 및 이상 시 즉시 대피</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1. 폭염 특보(35°C 이상) 발효 시 작업 일정 조정 및 오후 2~5시 야외 작업 최소화
+2. 시원한 휴식공간 마련 및 물·이온음료 상시 비치
+3. 작업자 1인당 1시간 이상 휴식 부여 및 현장 책임자 주기 순찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>한파 시 저온 환경에서 장시간 작업 중 저체온증·동상 등 한랭질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 한파 특보 확인</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1. 한파 특보(-15°C 이하) 발효 시 야외 노출 시간 최소화 및 방한복 지급
+2. 정기적인 휴식 시간 부여 및 실내 대피 장소 마련
+3. 작업자 이상 징후(오한, 손발 감각 저하) 발생 시 즉시 작업 중단</t>
         </is>
       </c>
     </row>
@@ -1196,406 +1406,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>중공종</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>위험요인(위험성평가)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>기존대책(미사용)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>빈도</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>강도</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>기존등급(미사용)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>위험성평가 개선대책</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>지하 작업 중 낙하물에 의한 사고위험</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 확인 및 제거</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1. 굴착 상단부에 자재 및 공구 적재 금지
-2. 하부 작업 시 상부 타 공정 혼재 작업 원칙적 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>소형 장비(탐상기 등) 수작업 운반 중 계단/비계에서 추락 및 전도</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>전용 수납가방 활용으로 양손 확보 및 3점 지지 승강 철저</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1. 장비 전용 수납가방 사용으로 이동 시 양손 확보
-2. 사다리/비계 승강 시 3점 지지 철저</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>배관 상부 등 고소작업 시 소형 장비(탐상기, 겔 등) 하부 낙하</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>장비 낙하방지끈 체결 및 하부 작업자 접근 통제</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1. 배관 탑승 작업 시 탐상기 및 공구 낙하방지끈 체결
-2. 작업 구역 하부 근로자 접근 전면 통제</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>근로자가 안전모 등 개인 보호구 미착용에 의한 충돌</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>현장 투입 전 개인보호구 착용 및 안전모 턱끈 자체 체결 확인</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1. 작업구역 진입 전 개인보호구 착용 상태 점검
-2. 안전모 턱끈 결속 철저</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>사전준비</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>중장비 주변 이동 중 장비와 충돌 또는 끼임</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>운전원과 직접 Eye Contact 및 수신호 교환 후 통행</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1. 장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
-2. 부득이하게 장비 주변 이동 시 운전원과 눈맞춤 및 수신호 확인 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>협소공간 검사 시 부자연스런 자세에 의한 근골격계질환 위험</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>작업 전 스트레칭</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1. 작업 전·후 전신 스트레칭 실시
-2. 장시간 구부린 자세 유지 시 주기적인 휴식(10분 이상) 부여</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>비파괴검사</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>우천으로 인한 굴착법면상태 악화에 의한 붕괴 위험</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 현상 일일 점검
-2. 호우 경보 발효 시 굴착 지점 내부 진입 전면 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>작업 후 정리</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>검사 완료 후 장비 반출 시 계단/비계에서 추락 및 전도</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>장비 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1. 반출 시 장비를 손에 쥐고 이동하는 행위 절대 금지
-2. 전용 가방 수납 후 3점 지지 하강 원칙 준수</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>작업 후 정리</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>장비 반출 중 수작업 인계 시 하부로 장비 낙하</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>하부 조원에게 직접 수작업 인계 및 장비 투척 절대 금지</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1. 2인 1조 작업으로 하부 조원에게 안전하게 수작업 인계
-2. 장비를 바닥으로 휙 던지는 행위 절대 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>작업 후 정리</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
-2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1692,7 +1502,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>소형 자재(스프레이, 세척액 등) 수작업 운반 중 추락/전도</t>
+          <t>소형 장비(탐상기 등) 수작업 운반 중 계단/비계에서 추락 및 전도</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1713,7 +1523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. 스프레이 등 탐상 자재 전용 포켓/가방에 수납
+          <t>1. 장비 전용 수납가방 사용으로 이동 시 양손 확보
 2. 사다리/비계 승강 시 3점 지지 철저</t>
         </is>
       </c>
@@ -1726,12 +1536,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>배관 상부 등 고소작업 시 스프레이 캔 하부 낙하</t>
+          <t>배관 상부 등 고소작업 시 소형 장비(탐상기, 겔 등) 하부 낙하</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>작업 구역 하부 접근 통제 및 잔여 자재 안전한 곳에 비치</t>
+          <t>장비 낙하방지끈 체결 및 하부 작업자 접근 통제</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1747,8 +1557,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. 비계나 배관 위 작업 시 스프레이가 굴러떨어지지 않도록 조치
-2. 하부 근로자 통행 전면 금지</t>
+          <t>1. 배관 탑승 작업 시 탐상기 및 공구 낙하방지끈 체결
+2. 작업 구역 하부 근로자 접근 전면 통제</t>
         </is>
       </c>
     </row>
@@ -1828,16 +1638,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>대상 화학물질에 대한 유해위험성 미인식에 의한 건강장해 발생 위험</t>
+          <t>협소공간 검사 시 부자연스런 자세에 의한 근골격계질환 위험</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>침투탐상제 취급 전 MSDS 유해성 자체 숙지 및 전파</t>
+          <t>작업 전 스트레칭</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1849,8 +1659,8 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1. 침투탐상제(세척액, 침투액, 현상액) MSDS 비치
-2. 작업 전 특별 안전보건 교육 실시 및 취급 주의 전파</t>
+          <t>1. 작업 전·후 전신 스트레칭 실시
+2. 장시간 구부린 자세 유지 시 주기적인 휴식(10분 이상) 부여</t>
         </is>
       </c>
     </row>
@@ -1862,97 +1672,97 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>화학물질 취급작업시 보호구 미착용으로 인한 사고 위험</t>
+          <t>우천으로 인한 굴착법면상태 악화에 의한 붕괴 위험</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>화학물질 취급 전 내화학 장갑/마스크 자체 수령 및 착용</t>
+          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1. 내화학 장갑 및 방독마스크 지급 및 착용 의무화
-2. 보호구 훼손 시 즉시 새 제품으로 교체 지급</t>
+          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 현상 일일 점검
+2. 호우 경보 발효 시 굴착 지점 내부 진입 전면 금지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비파괴검사</t>
+          <t>작업 후 정리</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>협소공간 검사 시 부자연스런 자세에 의한 근골격계질환 위험</t>
+          <t>검사 완료 후 장비 반출 시 계단/비계에서 추락 및 전도</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>작업 전 스트레칭</t>
+          <t>장비 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1. 작업 전·후 전신 스트레칭 실시
-2. 장시간 구부린 자세 유지 시 주기적인 휴식 부여</t>
+          <t>1. 반출 시 장비를 손에 쥐고 이동하는 행위 절대 금지
+2. 전용 가방 수납 후 3점 지지 하강 원칙 준수</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비파괴검사</t>
+          <t>작업 후 정리</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우천으로 인한 굴착법면상태 악화에 의한 붕괴 위험</t>
+          <t>장비 반출 중 수작업 인계 시 하부로 장비 낙하</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
+          <t>하부 조원에게 직접 수작업 인계 및 장비 투척 절대 금지</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 일일 점검
-2. 호우 경보 시 굴착 지점 내부 진입 전면 금지</t>
+          <t>1. 2인 1조 작업으로 하부 조원에게 안전하게 수작업 인계
+2. 장비를 바닥으로 휙 던지는 행위 절대 금지</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1774,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>검사 완료 후 자재 반출 시 계단/비계에서 추락 및 전도</t>
+          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>자재를 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
+          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1980,30 +1790,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1. 다 쓴 스프레이 캔 등을 손에 쥐고 이동 금지
-2. 빈 캔은 가방에 회수 후 3점 지지 하강 원칙 준수</t>
+          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
+2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>작업 후 정리</t>
+          <t>작업환경</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>자재 반출 중 수작업 인계 시 하부로 스프레이 캔 낙하</t>
+          <t>폭염 시 야외 작업 중 열사병·열탈진 등 온열질환 발생 위험</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>하부 조원에게 직접 수작업 인계 및 폐캔 투척 절대 금지</t>
+          <t>작업 전 기상청 폭염 특보 확인 및 이상 시 즉시 대피</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2019,25 +1829,26 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1. 하부 조원에게 빈 캔을 건네줄 때 안전하게 손으로 인계
-2. 사용이 끝난 빈 캔 바닥 투척 절대 금지</t>
+          <t>1. 폭염 특보(35°C 이상) 발효 시 작업 일정 조정 및 오후 2~5시 야외 작업 최소화
+2. 시원한 휴식공간 마련 및 물·이온음료 상시 비치
+3. 작업자 1인당 1시간 이상 휴식 부여 및 현장 책임자 주기 순찰</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>작업 후 정리</t>
+          <t>작업환경</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
+          <t>한파 시 저온 환경에서 장시간 작업 중 저체온증·동상 등 한랭질환 발생 위험</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
+          <t>작업 전 기상청 한파 특보 확인</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2048,13 +1859,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
-2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
+          <t>1. 한파 특보(-15°C 이하) 발효 시 야외 노출 시간 최소화 및 방한복 지급
+2. 정기적인 휴식 시간 부여 및 실내 대피 장소 마련
+3. 작업자 이상 징후(오한, 손발 감각 저하) 발생 시 즉시 작업 중단</t>
         </is>
       </c>
     </row>
@@ -2063,13 +1875,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2121,6 +1933,544 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>지하 작업 중 낙하물에 의한 사고위험</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>하부 진입 전 작업자가 상단부 낙하위험물 직접 확인 및 제거</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1. 굴착 상단부에 자재 및 공구 적재 금지
+2. 하부 작업 시 상부 타 공정 혼재 작업 원칙적 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>소형 자재(스프레이, 세척액 등) 수작업 운반 중 추락/전도</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>전용 수납가방 활용으로 양손 확보 및 3점 지지 승강 철저</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1. 스프레이 등 탐상 자재 전용 포켓/가방에 수납
+2. 사다리/비계 승강 시 3점 지지 철저</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>배관 상부 등 고소작업 시 스프레이 캔 하부 낙하</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>작업 구역 하부 접근 통제 및 잔여 자재 안전한 곳에 비치</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1. 비계나 배관 위 작업 시 스프레이가 굴러떨어지지 않도록 조치
+2. 하부 근로자 통행 전면 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>근로자가 안전모 등 개인 보호구 미착용에 의한 충돌</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>현장 투입 전 개인보호구 착용 및 안전모 턱끈 자체 체결 확인</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1. 작업구역 진입 전 개인보호구 착용 상태 점검
+2. 안전모 턱끈 결속 철저</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>사전준비</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>중장비 주변 이동 중 장비와 충돌 또는 끼임</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>운전원과 직접 Eye Contact 및 수신호 교환 후 통행</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1. 장비 가동 중 작업 반경 내 진입 절대 금지 및 우회 통로 이용
+2. 부득이하게 장비 주변 이동 시 운전원과 눈맞춤 및 수신호 확인 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>협소공간 검사 시 부자연스런 자세에 의한 근골격계질환 위험</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>작업 전 스트레칭</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1. 작업 전·후 전신 스트레칭 실시
+2. 장시간 구부린 자세 유지 시 주기적인 휴식 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>우천으로 인한 굴착법면상태 악화에 의한 붕괴 위험</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>지하 진입 전 법면 균열/용수(물비침) 자체 육안 점검</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1. 작업 전 굴착 법면 균열, 용수(물비침) 일일 점검
+2. 호우 경보 시 굴착 지점 내부 진입 전면 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>대상 화학물질에 대한 유해위험성 미인식에 의한 건강장해 발생 위험</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>침투탐상제 취급 전 MSDS 유해성 자체 숙지 및 전파</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1. 침투탐상제(세척액, 침투액, 현상액) MSDS 비치
+2. 작업 전 특별 안전보건 교육 실시 및 취급 주의 전파</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비파괴검사</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>화학물질 취급작업시 보호구 미착용으로 인한 사고 위험</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>화학물질 취급 전 내화학 장갑/마스크 자체 수령 및 착용</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1. 내화학 장갑 및 방독마스크 지급 및 착용 의무화
+2. 보호구 훼손 시 즉시 새 제품으로 교체 지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>작업 후 정리</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>검사 완료 후 자재 반출 시 계단/비계에서 추락 및 전도</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>자재를 전용 가방 수납 후 양손 확보 상태로 안전하게 하강</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1. 다 쓴 스프레이 캔 등을 손에 쥐고 이동 금지
+2. 빈 캔은 가방에 회수 후 3점 지지 하강 원칙 준수</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>작업 후 정리</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>자재 반출 중 수작업 인계 시 하부로 스프레이 캔 낙하</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>하부 조원에게 직접 수작업 인계 및 폐캔 투척 절대 금지</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1. 하부 조원에게 빈 캔을 건네줄 때 안전하게 손으로 인계
+2. 사용이 끝난 빈 캔 바닥 투척 절대 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>작업 후 정리</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>중장비 주변 이동 및 철수 중 장비와 충돌사고 위험</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>운전원과 수신호 확인 및 자체 동승자 하차 차량 유도</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1. 장비 철수 동선 파악 및 작업 반경 밖으로 우회 통행 철저
+2. 장비 주변 비파괴 자체 차량 이동 시 동승자가 하차하여 직접 유도</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>폭염 시 야외 작업 중 열사병·열탈진 등 온열질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 폭염 특보 확인 및 이상 시 즉시 대피</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1. 폭염 특보(35°C 이상) 발효 시 작업 일정 조정 및 오후 2~5시 야외 작업 최소화
+2. 시원한 휴식공간 마련 및 물·이온음료 상시 비치
+3. 작업자 1인당 1시간 이상 휴식 부여 및 현장 책임자 주기 순찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>한파 시 저온 환경에서 장시간 작업 중 저체온증·동상 등 한랭질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 한파 특보 확인</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1. 한파 특보(-15°C 이하) 발효 시 야외 노출 시간 최소화 및 방한복 지급
+2. 정기적인 휴식 시간 부여 및 실내 대피 장소 마련
+3. 작업자 이상 징후(오한, 손발 감각 저하) 발생 시 즉시 작업 중단</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>중공종</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>위험요인(위험성평가)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>기존대책(미사용)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>빈도</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>강도</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>기존등급(미사용)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>위험성평가 개선대책</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>반입 및 설치</t>
         </is>
       </c>
@@ -2319,6 +2669,76 @@
         <is>
           <t>1. 주기적인 환기(일 2회 이상) 실시
 2. 내부 화기 취급 금지 및 필요시 가스 감지기 설치</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>폭염 시 야외 작업 중 열사병·열탈진 등 온열질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 폭염 특보 확인 및 이상 시 즉시 대피</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1. 폭염 특보(35°C 이상) 발효 시 작업 일정 조정 및 오후 2~5시 야외 작업 최소화
+2. 시원한 휴식공간 마련 및 물·이온음료 상시 비치
+3. 작업자 1인당 1시간 이상 휴식 부여 및 현장 책임자 주기 순찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>작업환경</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>한파 시 저온 환경에서 장시간 작업 중 저체온증·동상 등 한랭질환 발생 위험</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>작업 전 기상청 한파 특보 확인</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1. 한파 특보(-15°C 이하) 발효 시 야외 노출 시간 최소화 및 방한복 지급
+2. 정기적인 휴식 시간 부여 및 실내 대피 장소 마련
+3. 작업자 이상 징후(오한, 손발 감각 저하) 발생 시 즉시 작업 중단</t>
         </is>
       </c>
     </row>
